--- a/api/assets/mock_collection.xlsx
+++ b/api/assets/mock_collection.xlsx
@@ -530,6 +530,9 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
+      <c r="H3" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,6 +555,11 @@
           <t>LP</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Reverse Holo</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -615,9 +623,14 @@
           <t>HP</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Holo</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -657,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
@@ -681,6 +694,11 @@
           <t>NM</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Reverse Holo, Misprint</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -713,14 +731,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -744,6 +762,11 @@
           <t>LP</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Shadowless</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -751,6 +774,9 @@
       </c>
       <c r="G10" t="n">
         <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="11">
@@ -782,9 +808,6 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -848,6 +871,9 @@
       <c r="G13" t="n">
         <v>1</v>
       </c>
+      <c r="H13" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -870,6 +896,11 @@
           <t>NM</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Reverse Holo</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -933,9 +964,14 @@
           <t>LP</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Holo</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -975,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18">
@@ -999,6 +1035,11 @@
           <t>HP</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Reverse Holo, Misprint</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1031,14 +1072,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -1062,6 +1103,11 @@
           <t>NM</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Shadowless</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -1069,6 +1115,9 @@
       </c>
       <c r="G20" t="n">
         <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="21">
@@ -1099,9 +1148,6 @@
       </c>
       <c r="G21" t="n">
         <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/api/assets/mock_collection.xlsx
+++ b/api/assets/mock_collection.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,7 +1147,116 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Base Set</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Charizard</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Holo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Gengar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Holo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Flareon</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
